--- a/server/internal/transport/http/docs/шаблон-техкарты.xlsx
+++ b/server/internal/transport/http/docs/шаблон-техкарты.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,11 @@
     <font>
       <color rgb="00006400"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -122,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -151,6 +156,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -534,6 +540,8 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,6 +620,16 @@
           <t>Шаг (г)</t>
         </is>
       </c>
+      <c r="P1" s="21" t="inlineStr">
+        <is>
+          <t>Вариация</t>
+        </is>
+      </c>
+      <c r="Q1" s="21" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -4719,6 +4737,420 @@
       </c>
       <c r="O71" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Пицца Пепперони (пример вариаций)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>hot_kitchen</t>
+        </is>
+      </c>
+      <c r="E72">
+        <f>SUMIF(Техкарты!A:A,C72,Техкарты!D:D)</f>
+        <v/>
+      </c>
+      <c r="F72">
+        <f>SUMIF(Техкарты!A:A,C72,Техкарты!G:G)</f>
+        <v/>
+      </c>
+      <c r="G72" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="H72">
+        <f>IF(G72&gt;0,F72/G72*100,0)</f>
+        <v/>
+      </c>
+      <c r="I72">
+        <f>IF(F72&gt;0,(G72-F72)/F72*100,0)</f>
+        <v/>
+      </c>
+      <c r="J72">
+        <f>COUNTIF(Техкарты!A:A,C72)</f>
+        <v/>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Размер</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Пицца Пепперони (пример вариаций)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>hot_kitchen</t>
+        </is>
+      </c>
+      <c r="E73">
+        <f>SUMIF(Техкарты!A:A,C73,Техкарты!D:D)</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>SUMIF(Техкарты!A:A,C73,Техкарты!G:G)</f>
+        <v/>
+      </c>
+      <c r="G73" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="H73">
+        <f>IF(G73&gt;0,F73/G73*100,0)</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>IF(F73&gt;0,(G73-F73)/F73*100,0)</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>COUNTIF(Техкарты!A:A,C73)</f>
+        <v/>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Размер</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Пицца Пепперони (пример вариаций)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>hot_kitchen</t>
+        </is>
+      </c>
+      <c r="E74">
+        <f>SUMIF(Техкарты!A:A,C74,Техкарты!D:D)</f>
+        <v/>
+      </c>
+      <c r="F74">
+        <f>SUMIF(Техкарты!A:A,C74,Техкарты!G:G)</f>
+        <v/>
+      </c>
+      <c r="G74" s="22" t="n">
+        <v>85</v>
+      </c>
+      <c r="H74">
+        <f>IF(G74&gt;0,F74/G74*100,0)</f>
+        <v/>
+      </c>
+      <c r="I74">
+        <f>IF(F74&gt;0,(G74-F74)/F74*100,0)</f>
+        <v/>
+      </c>
+      <c r="J74">
+        <f>COUNTIF(Техкарты!A:A,C74)</f>
+        <v/>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Размер</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Фанта (пример вариаций)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E75">
+        <f>SUMIF(Техкарты!A:A,C75,Техкарты!D:D)</f>
+        <v/>
+      </c>
+      <c r="F75">
+        <f>SUMIF(Техкарты!A:A,C75,Техкарты!G:G)</f>
+        <v/>
+      </c>
+      <c r="G75" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75">
+        <f>IF(G75&gt;0,F75/G75*100,0)</f>
+        <v/>
+      </c>
+      <c r="I75">
+        <f>IF(F75&gt;0,(G75-F75)/F75*100,0)</f>
+        <v/>
+      </c>
+      <c r="J75">
+        <f>COUNTIF(Техкарты!A:A,C75)</f>
+        <v/>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>0.5 л</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Фанта (пример вариаций)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E76">
+        <f>SUMIF(Техкарты!A:A,C76,Техкарты!D:D)</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>SUMIF(Техкарты!A:A,C76,Техкарты!G:G)</f>
+        <v/>
+      </c>
+      <c r="G76" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H76">
+        <f>IF(G76&gt;0,F76/G76*100,0)</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>IF(F76&gt;0,(G76-F76)/F76*100,0)</f>
+        <v/>
+      </c>
+      <c r="J76">
+        <f>COUNTIF(Техкарты!A:A,C76)</f>
+        <v/>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1 л</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Фанта (пример вариаций)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E77">
+        <f>SUMIF(Техкарты!A:A,C77,Техкарты!D:D)</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>SUMIF(Техкарты!A:A,C77,Техкарты!G:G)</f>
+        <v/>
+      </c>
+      <c r="G77" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77">
+        <f>IF(G77&gt;0,F77/G77*100,0)</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>IF(F77&gt;0,(G77-F77)/F77*100,0)</f>
+        <v/>
+      </c>
+      <c r="J77">
+        <f>COUNTIF(Техкарты!A:A,C77)</f>
+        <v/>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1.5 л</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23049,7 +23481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A97"/>
+  <dimension ref="A1:A124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -23329,7 +23761,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -23351,7 +23782,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
@@ -23450,7 +23880,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -23472,7 +23901,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -23508,12 +23936,8 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
+    <row r="72"/>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
@@ -23521,9 +23945,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -23538,9 +23960,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-    </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -23562,9 +23982,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-    </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -23579,9 +23997,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-    </row>
+    <row r="85"/>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
@@ -23596,9 +24012,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-    </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -23627,9 +24041,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
+    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -23655,6 +24067,167 @@
       <c r="A97" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Для kg    — за 1 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>── НОВОЕ: Вариации (размеры пицц, объёмы напитков) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Один продукт может продаваться в нескольких вариантах: пицца в размерах</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>25/30/35, напиток в объёмах 0.5/1/1.5 л. Для этого в листе «Блюда» есть</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>две колонки:</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Вариация — имя атрибута: «Размер» (пиццы), «Объём» (напитки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Значение — конкретный вариант: «25», «30», «35» или «0.5 л», «1 л», «1.5 л»</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Правила:</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Каждый вариант — отдельная строка с ОДИНАКОВЫМ названием блюда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Цена (колонка G) указывается в каждой строке — своя у каждого варианта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Категория/станция берутся из первой строки продукта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. «Доступно» = Да хотя бы в одной строке → продукт доступен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. До 10 значений на продукт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>При импорте строки с одинаковым названием схлопнутся в один продукт</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>с вариантами: на кассе выбор размера/объёма, у каждого варианта своя</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>цена и своя техкарта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Техкарты вариантов: в листе «Техкарты» пишите полное имя варианта —</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>«Пицца Пепперони 30», «Фанта 1 л» (название + значение через пробел).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Пример — см. последние строки листа «Блюда»: «Пицца Пепперони (пример</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>вариаций)» (Размер 25/30/35) и «Фанта (пример вариаций)» (Объём 0.5/1/1.5 л).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Перед импортом своего меню примерные строки удалите.</t>
         </is>
       </c>
     </row>

--- a/server/internal/transport/http/docs/шаблон-техкарты.xlsx
+++ b/server/internal/transport/http/docs/шаблон-техкарты.xlsx
@@ -19327,7 +19327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19338,6 +19338,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19379,6 +19380,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Используется в блюдах (шт.)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
         </is>
       </c>
     </row>
@@ -23481,7 +23487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A124"/>
+  <dimension ref="A1:A128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -24231,6 +24237,37 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>── НОВОЕ: Тип ингредиента (хозтовары) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>В листе «Ингредиенты» есть необязательная колонка «Тип» (I):</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>  Пусто или «Продукт» — обычный ингредиент (еда).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>  «Хозтовар» — одноразовая посуда, упаковка, салфетки и т.п. — попадает на склад «Хозтовары».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
